--- a/StyleOfDelivery/BCIO-style-hierarchy.xlsx
+++ b/StyleOfDelivery/BCIO-style-hierarchy.xlsx
@@ -441,14 +441,14 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Cross reference</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Informal definition</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Cross reference</t>
-        </is>
-      </c>
       <c r="I1" t="inlineStr">
         <is>
           <t>Examples</t>
@@ -456,12 +456,12 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>Synonyms</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Comment</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Synonyms</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
           <t>style of delivery</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Communication processes can have a variety of attributes, such as their speed, how they are delivered, what language they take place in and the tone of voice in which they occur.  All these types of attributes and more are captured by "communication process attribute"</t>
         </is>
@@ -497,72 +497,72 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BCIO:044004</t>
+          <t>BCIO:044130</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>communication style</t>
+          <t>readability</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>A particular manner of communicating aimed at inducing or avoiding certain kinds of responses in others, or demonstrating certain characteristics of the initiator.</t>
+          <t>An attribute of a text used in communication process, concerning the ease of understanding the wording or other qualitative aspects of the text that facilitate comprehension.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>including adequate blank space and empty circles for the young people and their carers to record and review agenda items</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BCIO:044098</t>
+          <t>BCIO:044004</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>didactic communication style</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>communication style</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>A communication style characterised by the initiator addressing the recipient in the manner of a teacher or lecturer.</t>
+          <t>A particular manner of communicating aimed at inducing or avoiding certain kinds of responses in others, or demonstrating certain characteristics of the initiator.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>gave a short lecture, conference presentation</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BCIO:044110</t>
+          <t>BCIO:044114</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>non-defensive communication style</t>
+          <t>persuasive communication style</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>A communication style characterised by suggesting the initiator is open to or able to accept criticism.</t>
+          <t>A communication style which aims to induce or urge the adoption of certain beliefs, theories or lines of action.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -574,125 +574,130 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCIO:050380</t>
+          <t>BCIO:044108</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>aggressive communication style</t>
+          <t>interactive communication style</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>A communication style characterised by aggression.</t>
+          <t>A communication style characterised by being responsive to the recipient's activity.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>interactive presentation</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCIO:050390</t>
+          <t>BCIO:044118</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>humorous communication style</t>
+          <t>responsive communication style</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>A communication style intended to amuse.</t>
+          <t>A communication style characterised by adapting to the views and behaviours of the recipient.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>This class is adapting response as a result of how another person is communicating. In contrast, respectful communication style involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:044121</t>
+          <t>BCIO:044103</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>theatrical communication style</t>
+          <t>entertaining communication style</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>A communication style similar to that used for dramatic performance or the theatre.</t>
+          <t>A communication style intended to be amusing or enjoyable for the recipient.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fun</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:044084</t>
+          <t>BCIO:044092</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>autonomy-supportive communication style</t>
+          <t>communication style conveying perceived superiority</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>A communication style which aims to promote the recipient's capacity to make their own decisions.</t>
+          <t>A communication style which imparts a feeling that the instigator believes themselves to be higher in status than the recipient.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">from Self-Determination Theory interventions. </t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>needs-supportive communication style</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:044087</t>
+          <t>BCIO:044086</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>communication style conveying acceptance</t>
+          <t>cold communication style</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>A communication style that conveys respect and regard for the recipient as an individual.</t>
+          <t>A communication style suggesting a lack of human interest or friendliness towards the recipient.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -704,130 +709,130 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:044118</t>
+          <t>BCIO:044085</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>responsive communication style</t>
+          <t>collaborative communication style</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>A communication style characterised by adapting to the views and behaviours of the recipient.</t>
+          <t>A communication style characterised by a sense of the initiator and recipient working together, the initiator showing sensitivity to the others' needs, in order to obtain an outcome desired by all.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>This class is adapting response as a result of how another person is communicating. In contrast, respectful communication style involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:044111</t>
+          <t>BCIO:044101</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>non-confrontational communication style</t>
+          <t>empathic communication style</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>A communication style characterised by being diplomatic and avoiding conflict.</t>
+          <t>A communication style which conveys an insightful awareness of the feelings and behaviours of the recipient.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>sensitivity, compassion</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:044117</t>
+          <t>BCIO:044104</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>respectful communication style</t>
+          <t>formal communication style</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>A communication style suggesting an understanding of and regard for the feelings, wishes, or rights of others.</t>
+          <t>A communication style characterised by the use of traditional standards of correctness and etiquette and without casual, contracted, or colloquial forms of language.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>"acknowledging the victim's feelings"</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">This class involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says.  In contrast, responsive communication style is adapting the response as a result of how another person is communicating. </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCIO:050381</t>
+          <t>BCIO:044117</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>angry communication style</t>
+          <t>respectful communication style</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>A communication style characterised by anger.</t>
+          <t>A communication style suggesting an understanding of and regard for the feelings, wishes, or rights of others.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>"acknowledging the victim's feelings"</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This class involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says.  In contrast, responsive communication style is adapting the response as a result of how another person is communicating. </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:044079</t>
+          <t>BCIO:044122</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>active participation encouraging communication style</t>
+          <t>verbally dominant communication style</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>A communication style marked by fostering the involvement of the recipient as an engaged actor in the activity to be undertaken rather than as a passive recipient.</t>
+          <t>A communication style characterised by one participant having more control over a conversation than the other.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -839,101 +844,101 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:050389</t>
+          <t>BCIO:044105</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>direct communication style</t>
+          <t>impatient communication style</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>A communication style characterised by the explicit presentation of information.</t>
+          <t>A communication style conveying feelings of annoyance at time taken to understand or complete a process.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Note that this class is different from directive communication style</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:044104</t>
+          <t>BCIO:044109</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>formal communication style</t>
+          <t>legitimising communication style</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>A communication style characterised by the use of traditional standards of correctness and etiquette and without casual, contracted, or colloquial forms of language.</t>
+          <t>A communication style characterised by making a person feel that their perspective or emotions are legitimate.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>validating emotions</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This entails a deliberate strategy to make the person feel their perspective is legitimate </t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:044103</t>
+          <t>BCIO:044097</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>entertaining communication style</t>
+          <t>conversational communication style</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>A communication style intended to be amusing or enjoyable for the recipient.</t>
+          <t>A communication style that is typical of interpersonal dialogue which encourages an interactive exchange of ideas and beliefs.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fun</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:044107</t>
+          <t>BCIO:044111</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>intellectual communication style</t>
+          <t>non-confrontational communication style</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>A communication style characterised by an emphasis on reasoning and promoting objective understanding.</t>
+          <t>A communication style characterised by being diplomatic and avoiding conflict.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -945,96 +950,106 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:044105</t>
+          <t>BCIO:044119</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>impatient communication style</t>
+          <t>semi-structured communication style</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>A communication style conveying feelings of annoyance at time taken to understand or complete a process.</t>
+          <t>A communication style involving the communication content having some constituent pre-planned parts but also being responsive to inputs.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Using talking points, using conversation guides, having a list of topics to cover</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>organised communication style</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:044085</t>
+          <t>BCIO:044000</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>collaborative communication style</t>
+          <t>behaviour change intervention style of delivery</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>A communication style characterised by a sense of the initiator and recipient working together, the initiator showing sensitivity to the others' needs, in order to obtain an outcome desired by all.</t>
+          <t>A communication style that is an attribute of a BCI content communication process.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>when a communication style is used as part of a BCI content communication process, then it qualifies as a BCI style of delivery</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:044091</t>
+          <t>BCIO:050381</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>communication style conveying hopefulness</t>
+          <t>angry communication style</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>A communication style which imparts a feeling of optimism that a person will attain a desired outcome.</t>
+          <t>A communication style characterised by anger.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>optimism, positivity</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:044119</t>
+          <t>BCIO:044113</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>semi-structured communication style</t>
+          <t>patient communication style</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>A communication style involving the communication content having some constituent pre-planned parts but also being responsive to inputs.</t>
+          <t>A communication style conveying willingness to take time to understand or complete a process.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1044,12 +1059,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Using talking points, using conversation guides, having a list of topics to cover</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>organised communication style</t>
+          <t>"willing to listen"</t>
         </is>
       </c>
     </row>
@@ -1080,43 +1090,48 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:044095</t>
+          <t>BCIO:044106</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>communication style demonstrating positive regard</t>
+          <t>informal communication style</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>A communication style demonstrating acceptance of everything about the recipient.</t>
+          <t>A communication style characterised by the use of casual or colloquial language rather than formal language.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>"Colloquial" language is language that is typically used in ordinary conversation rather than in formal communication</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:044116</t>
+          <t>BCIO:044091</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>relaxed communication style</t>
+          <t>communication style conveying hopefulness</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>A communication style characterised by a lack of tension or anxiety.</t>
+          <t>A communication style which imparts a feeling of optimism that a person will attain a desired outcome.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1124,52 +1139,57 @@
           <t>style of delivery</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>calm communication style</t>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>optimism, positivity</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:044092</t>
+          <t>BCIO:044005</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>communication style conveying perceived superiority</t>
+          <t>intervention style of delivery</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>A communication style which imparts a feeling that the instigator believes themselves to be higher in status than the recipient.</t>
+          <t>A communication style that is an attribute of an intervention content communication process.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>when a communication style is used as part of an intervention content communication process, then it qualifies as an intervention style of delivery</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:044106</t>
+          <t>BCIO:044116</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>informal communication style</t>
+          <t>relaxed communication style</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>A communication style characterised by the use of casual or colloquial language rather than formal language.</t>
+          <t>A communication style characterised by a lack of tension or anxiety.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1179,31 +1199,41 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>"Colloquial" language is language that is typically used in ordinary conversation rather than in formal communication</t>
+          <t>calm communication style</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:044096</t>
+          <t>BCIO:044084</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>controlling communication style</t>
+          <t>autonomy-supportive communication style</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>A communication style which directly instructs the adoption of certain beliefs, theories or lines of action.</t>
+          <t>A communication style which aims to promote the recipient's capacity to make their own decisions.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>needs-supportive communication style</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">from Self-Determination Theory interventions. </t>
         </is>
       </c>
     </row>
@@ -1232,31 +1262,31 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t>standardised</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">This class is pre-planned style but not to the extent of using a written script. In contrast, "Script-based communication" involves tightly following a set of written instructions. </t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>standardised</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:044083</t>
+          <t>BCIO:044090</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>attentive communication style</t>
+          <t>communication style conveying genuineness</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>A communication style characterised by purposeful consideration of another's statements.</t>
+          <t>A communication style which suggests one is acting in line with one's true values and beliefs.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1264,33 +1294,28 @@
           <t>style of delivery</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>"listened carefully to what you had to say"</t>
-        </is>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">This involves communicating in a manner that ensures the recipient knows that they are being heard </t>
+          <t>sincerity</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:044115</t>
+          <t>BCIO:044110</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>polite communication style</t>
+          <t>non-defensive communication style</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>A communication style characterised by courtesy.</t>
+          <t>A communication style characterised by suggesting the initiator is open to or able to accept criticism.</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1302,19 +1327,19 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:044101</t>
+          <t>BCIO:044083</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>empathic communication style</t>
+          <t>attentive communication style</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>A communication style which conveys an insightful awareness of the feelings and behaviours of the recipient.</t>
+          <t>A communication style characterised by purposeful consideration of another's statements.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1322,86 +1347,81 @@
           <t>style of delivery</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>"listened carefully to what you had to say"</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>sensitivity, compassion</t>
+          <t xml:space="preserve">This involves communicating in a manner that ensures the recipient knows that they are being heard </t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:044113</t>
+          <t>BCIO:044112</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>patient communication style</t>
+          <t>non-judgmental communication style</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>A communication style conveying willingness to take time to understand or complete a process.</t>
+          <t>A communication style that demonstrates that one is not assigning a positive or negative valence to another's views or behaviours.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>"willing to listen"</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:044082</t>
+          <t>BCIO:044102</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>articulate communication style</t>
+          <t>engaging communication style</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>A communication style characterised by the initiator fluently using language to express ideas.</t>
+          <t>A communication style characterised by attempting to attract and maintain a recipient's interest or attention.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> fluent</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:044094</t>
+          <t>BCIO:044087</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>communication style conveying support for change</t>
+          <t>communication style conveying acceptance</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>A communication style which imparts one's belief that the recipient can change.</t>
+          <t>A communication style that conveys respect and regard for the recipient as an individual.</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1413,130 +1433,125 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:044109</t>
+          <t>BCIO:044107</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>legitimising communication style</t>
+          <t>intellectual communication style</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>A communication style characterised by making a person feel that their perspective or emotions are legitimate.</t>
+          <t>A communication style characterised by an emphasis on reasoning and promoting objective understanding.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">This entails a deliberate strategy to make the person feel their perspective is legitimate </t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>validating emotions</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:044102</t>
+          <t>BCIO:050389</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>engaging communication style</t>
+          <t>direct communication style</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>A communication style characterised by attempting to attract and maintain a recipient's interest or attention.</t>
+          <t>A communication style characterised by the explicit presentation of information.</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Note that this class is different from directive communication style</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:044097</t>
+          <t>BCIO:044123</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>conversational communication style</t>
+          <t>warm communication style</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>A communication style that is typical of interpersonal dialogue which encourages an interactive exchange of ideas and beliefs.</t>
+          <t>A communication style which demonstrates human interest and caring.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>friendly communication style</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:044090</t>
+          <t>BCIO:044079</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>communication style conveying genuineness</t>
+          <t>active participation encouraging communication style</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>A communication style which suggests one is acting in line with one's true values and beliefs.</t>
+          <t>A communication style marked by fostering the involvement of the recipient as an engaged actor in the activity to be undertaken rather than as a passive recipient.</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>sincerity</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:044100</t>
+          <t>BCIO:044098</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>easily comprehended communication style</t>
+          <t>didactic communication style</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>A communication style characterised by using language in a manner intended to be easily understandable to a recipient.</t>
+          <t>A communication style characterised by the initiator addressing the recipient in the manner of a teacher or lecturer.</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1546,31 +1561,26 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>using non-technical language, using clear language, avoiding jargon</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>This can involve using plain and simple language</t>
+          <t>gave a short lecture, conference presentation</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:050391</t>
+          <t>BCIO:044115</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>non-responsive communication style</t>
+          <t>polite communication style</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>A communication style characterised by not adapting to the views and behaviours of the recipient.</t>
+          <t>A communication style characterised by courtesy.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1606,19 +1616,19 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:044122</t>
+          <t>BCIO:044096</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>verbally dominant communication style</t>
+          <t>controlling communication style</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>A communication style characterised by one participant having more control over a conversation than the other.</t>
+          <t>A communication style which directly instructs the adoption of certain beliefs, theories or lines of action.</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1630,19 +1640,19 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:044112</t>
+          <t>BCIO:050380</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>non-judgmental communication style</t>
+          <t>aggressive communication style</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>A communication style that demonstrates that one is not assigning a positive or negative valence to another's views or behaviours.</t>
+          <t>A communication style characterised by aggression.</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1654,19 +1664,19 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:044114</t>
+          <t>BCIO:044094</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>persuasive communication style</t>
+          <t>communication style conveying support for change</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>A communication style which aims to induce or urge the adoption of certain beliefs, theories or lines of action.</t>
+          <t>A communication style which imparts one's belief that the recipient can change.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1678,19 +1688,19 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:044108</t>
+          <t>BCIO:044100</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>interactive communication style</t>
+          <t>easily comprehended communication style</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>A communication style characterised by being responsive to the recipient's activity.</t>
+          <t>A communication style characterised by using language in a manner intended to be easily understandable to a recipient.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1700,26 +1710,31 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>interactive presentation</t>
+          <t>using non-technical language, using clear language, avoiding jargon</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>This can involve using plain and simple language</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:044086</t>
+          <t>BCIO:044095</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>cold communication style</t>
+          <t>communication style demonstrating positive regard</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>A communication style suggesting a lack of human interest or friendliness towards the recipient.</t>
+          <t>A communication style demonstrating acceptance of everything about the recipient.</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1731,19 +1746,19 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:044099</t>
+          <t>BCIO:044082</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>directive communication style</t>
+          <t>articulate communication style</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>A communication style intended to play an active role in another person's decision making.</t>
+          <t>A communication style characterised by the initiator fluently using language to express ideas.</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1751,33 +1766,28 @@
           <t>style of delivery</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>http://purl.bioontology.org/ontology/MESH/D037001</t>
-        </is>
-      </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Note that this class is different from direct communication style</t>
+          <t xml:space="preserve"> fluent</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:044081</t>
+          <t>BCIO:044121</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>aloof communication style</t>
+          <t>theatrical communication style</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>A communication style characterised by a lack of empathy or compassion for the recipient.</t>
+          <t>A communication style similar to that used for dramatic performance or the theatre.</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -1789,77 +1799,67 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:044123</t>
+          <t>BCIO:044089</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>warm communication style</t>
+          <t>communication style conveying concern</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>A communication style which demonstrates human interest and caring.</t>
+          <t>A communication style demonstrating one perceives an unwanted circumstance for the recipient.</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>friendly communication style</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:044005</t>
+          <t>BCIO:050390</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>intervention style of delivery</t>
+          <t>humorous communication style</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>A communication style that is an attribute of an intervention content communication process.</t>
+          <t>A communication style intended to amuse.</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>when a communication style is used as part of an intervention content communication process, then it qualifies as an intervention style of delivery</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:044089</t>
+          <t>BCIO:044081</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>communication style conveying concern</t>
+          <t>aloof communication style</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>A communication style demonstrating one perceives an unwanted circumstance for the recipient.</t>
+          <t>A communication style characterised by a lack of empathy or compassion for the recipient.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -1871,19 +1871,19 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:044000</t>
+          <t>BCIO:044099</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>behaviour change intervention style of delivery</t>
+          <t>directive communication style</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>A communication style that is an attribute of a BCI content communication process.</t>
+          <t>A communication style intended to play an active role in another person's decision making.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -1891,38 +1891,38 @@
           <t>style of delivery</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>when a communication style is used as part of a BCI content communication process, then it qualifies as a BCI style of delivery</t>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>http://purl.bioontology.org/ontology/MESH/D037001</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Note that this class is different from direct communication style</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:044127</t>
+          <t>BCIO:050391</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>object visual style</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>non-responsive communication style</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>An attribute of an object used in a communication process, concerning how information sensed with the eyes is presented, which may include colours/fonts/images/spacing/sizing.</t>
+          <t>A communication style characterised by not adapting to the views and behaviours of the recipient.</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>colour scheme chosen for a website, style of images used for a booklet, brightly coloured reminder stickers</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
           <t>arrangement of chairs in the room for a group intervention, amount of space between blocks of text in a leaflet, arrangement of sections of a website</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>the arrangement of components can be deliberately chosen to help communicate intervention content</t>
         </is>
@@ -1988,7 +1988,7 @@
           <t>Health care professionals' uniform to convey authority and knowledge, doctors not wearing white coats to speak to children</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>may be purposefully chosen to convey certain attributes of the source</t>
         </is>
@@ -2021,19 +2021,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:044130</t>
+          <t>BCIO:044127</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>readability</t>
+          <t>object visual style</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>An attribute of a text used in communication process, concerning the ease of understanding the wording or other qualitative aspects of the text that facilitate comprehension.</t>
+          <t>An attribute of an object used in a communication process, concerning how information sensed with the eyes is presented, which may include colours/fonts/images/spacing/sizing.</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>including adequate blank space and empty circles for the young people and their carers to record and review agenda items</t>
+          <t>colour scheme chosen for a website, style of images used for a booklet, brightly coloured reminder stickers</t>
         </is>
       </c>
     </row>
@@ -2074,19 +2074,19 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:050555</t>
+          <t>BCIO:045000</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>communication message</t>
+          <t>intervention delivery</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>An &lt;information content entity&gt; transmitted from a communication source to a communication recipient.</t>
+          <t>A planned process by which intervention content is delivered.</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2098,19 +2098,19 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:050553</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>communication recipient</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>BCIO:044006</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>person-centred intervention delivery</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>A &lt;person&gt; who receives a communication.</t>
+          <t>An intervention delivery characterised by efforts by an intervention source to give a person the resources they need to manage their own life and make them an active participant in deciding how to move forward.</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2122,19 +2122,19 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:050457</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>expressive behaviour</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>BCIO:008000</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>behaviour change intervention delivery</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>An individual human behaviour that conveys a thought or feeling.</t>
+          <t>An intervention delivery in which the intervention is a behaviour change intervention.</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2146,43 +2146,38 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:036034</t>
+          <t>BCIO:044008</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>human communication behaviour</t>
+          <t>source-led intervention delivery</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>An expressive behaviour that involves the transmission of information between two or more people.</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An intervention delivery in which the intervention person source takes the lead in determining the focus of the intervention.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:050237</t>
+          <t>BCIO:044007</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>linguistic communication behaviour</t>
-        </is>
-      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>participant-led intervention delivery</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>A human communication behaviour in which the information that is communicated is encoded in language.</t>
+          <t>An intervention delivery in which the participant takes the lead in determining the focus of the intervention.</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2194,19 +2189,19 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:050374</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>laughing</t>
-        </is>
-      </c>
+          <t>BCIO:050553</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>communication recipient</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>An expressive behaviour showing elation, amusement or scorn by means of facial expressions and repeated sharp exhalations.</t>
+          <t>A &lt;person&gt; who receives a communication.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2218,19 +2213,19 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:045000</t>
+          <t>BCIO:050554</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>intervention delivery</t>
+          <t>communication source</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>A planned process by which intervention content is delivered.</t>
+          <t>A &lt;material entity&gt; that originates a communication.</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2242,19 +2237,19 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:044007</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>participant-led intervention delivery</t>
-        </is>
-      </c>
+          <t>BCIO:036025</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>inter-personal behaviour</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>An intervention delivery in which the participant takes the lead in determining the focus of the intervention.</t>
+          <t>An &lt;socially-related behaviour&gt; that involves an interaction between two or more people.</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2266,86 +2261,101 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:008000</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>behaviour change intervention delivery</t>
-        </is>
-      </c>
+          <t>BCIO:050384</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>communication</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>An intervention delivery in which the intervention is a behaviour change intervention.</t>
+          <t>A process involving the transmission of information between two or more participants.</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>The participants in the communication process can be of a variety of types, e.g. a human talking to an automated chatbot system, two computer systems exchanging information, a person talking to a pet animal etc.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:044006</t>
+          <t>BCIO:044043</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>person-centred intervention delivery</t>
+          <t>communication using a particular form of address</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>An intervention delivery characterised by efforts by an intervention source to give a person the resources they need to manage their own life and make them an active participant in deciding how to move forward.</t>
+          <t>A communication addressing a person using a certain name or title to refer to that person.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
           <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>The child classes of this class are specific types of address, whereas this class is for a non-specific type of address.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BCIO:044008</t>
+          <t>BCIO:044045</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>source-led intervention delivery</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>communication using informal address</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>An intervention delivery in which the intervention person source takes the lead in determining the focus of the intervention.</t>
+          <t>A communication addressing a person using a casual or colloquial name or title to refer to that person.</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BCIO:036025</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>inter-personal behaviour</t>
-        </is>
-      </c>
+          <t>BCIO:044044</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>communication using formal address</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>An &lt;socially-related behaviour&gt; that involves an interaction between two or more people.</t>
+          <t>A communication addressing a person using a formal, legal or official name or title to refer to that person.</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2357,43 +2367,48 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BCIO:050554</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>communication source</t>
-        </is>
-      </c>
+          <t>BCIO:044046</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>communication using preferred form of address</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>A &lt;material entity&gt; that originates a communication.</t>
+          <t>A communication addressing a person using a name or title that the person has specified the instigator should use.</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Depending on whether Suzie Jones prefers to be addressed formally, or by her given name, saying either "Hello Mrs Jones" or "Hello Suzie"</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BCIO:050384</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>communication</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>BCIO:044070</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>paraphrasing</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>A process involving the transmission of information between two or more participants.</t>
+          <t>A communication in which one participant summarises what the other said.</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2401,28 +2416,28 @@
           <t>style of delivery</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>The participants in the communication process can be of a variety of types, e.g. a human talking to an automated chatbot system, two computer systems exchanging information, a person talking to a pet animal etc.</t>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>This class is different to "communication involving confirmatory rephrasing" as this class is simply about summarising what another person said.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BCIO:044070</t>
+          <t>BCIO:044029</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>paraphrasing</t>
+          <t>communication evoking another's ideas about change</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>A communication in which one participant summarises what the other said.</t>
+          <t>A communication in which the initiator attempts to elicit the recipient’s own thoughts and ideas about change rather than imposing the initiator’s own opinion.</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2432,50 +2447,45 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>This class is different to "communication involving confirmatory rephrasing" as this class is simply about summarising what another person said.</t>
+          <t>evoking change talk in motivational interviewing</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BCIO:044059</t>
+          <t>BCIO:044040</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>emotionally expressive communication</t>
+          <t>communication involving elaboration of arguments</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>A communication in a manner which clearly conveys the emotions of the initiator.</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication further developing a declarative statement that has been made  by making it clearer, more precise, bringing out its consequences or giving a concrete example.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BCIO:044124</t>
+          <t>BCIO:044030</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>relationship building</t>
+          <t>exploring communication</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>A communication aimed at building or managing aspects of the interpersonal relationship between an initiator and a recipient rather than focusing on delivering communication content.</t>
+          <t>A communication to better understand what a person thinks or feels about a topic or an experience.</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2485,26 +2495,31 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>offering contact, inviting patient to contact you in the event of difficulties or questions</t>
+          <t>eliciting or seeking information</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>This can include asking questions or prompting elaboration e.g 'Tell me more about that'</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BCIO:044017</t>
+          <t>BCIO:050383</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>banter</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>communication exploring a person's feelings about a topic</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>A communication involving the exchange of light and teasing remarks intended to be playful.</t>
+          <t>An exploring communication focused on a person's affective responses to a matter.</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2512,28 +2527,28 @@
           <t>style of delivery</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Note that teasing is an essential part of the definition of banter. For amusing or enjoyable communication, but without the element of teasing, using entertaining or humourous communication style. Also, note that banter may not always be perceived as playful by the subject of the remarks</t>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Elicit concerns, problems and reactions</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BCIO:044049</t>
+          <t>BCIO:050387</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>communication using interjections to signal attentiveness</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>communication exploring a person's thoughts about an experience</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>A communication in which one person uses brief interjections to signal that they are listening to what the other person is saying.</t>
+          <t>An exploring communication focused on what a person thinks about an experience.</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2541,81 +2556,86 @@
           <t>style of delivery</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Words like "interesting", "yeah"," mmhmm"</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>An interjection is a word, phrase or exclamation which is typically unconnected to a sentence and is used to express an emotion or reaction.</t>
-        </is>
-      </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>"Back-channels" or "undertalk" in the Roter Interaction Analysis System</t>
+          <t>An experience can be any situation or state a person encounters or undergoes</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BCIO:044058</t>
+          <t>BCIO:050385</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>communication using rational arguments</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>communication exploring a person's feelings about an experience</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>A communication that involves the use of declarative propositions based on what the communicator believes to be logical.</t>
+          <t>An exploring communication focused on a person's affective responses to an experience.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>An experience can be any situation or state a person encounters or undergoes</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BCIO:044023</t>
+          <t>BCIO:050386</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>communication asking permission to provide information and advice</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>communication exploring a person's thoughts about a topic</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>A communication which involves asking for approval before sharing knowledge and giving guidance.</t>
+          <t>An exploring communication focused on what a person thinks about a matter.</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>clarifying what someone has said</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BCIO:044050</t>
+          <t>BCIO:044065</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>communication using particular language</t>
+          <t>negotiation</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>A communication using certain vocabulary or phraseology.</t>
+          <t>A communication involving goal-oriented collaboration to arrive at an agreement or compromise on a matter of importance to the individuals involved.</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -2627,19 +2647,19 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BCIO:044055</t>
+          <t>BCIO:044050</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>communication avoiding offensive language</t>
-        </is>
-      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>communication using particular language</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>A communication using language chosen by the instigator to avoid using words or phrases that could be perceived as rude or insulting.</t>
+          <t>A communication using certain vocabulary or phraseology.</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -2699,48 +2719,43 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BCIO:044054</t>
+          <t>BCIO:044052</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>communication using specialist language</t>
+          <t>communication using non-pressurising language</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>A communication using words or expressions used by a profession or group that are difficult for others not in that profession or group to understand.</t>
+          <t>A communication using language chosen to avoid coercing or persuading the recipient to think, feel or behave in a certain manner.</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>using jargon</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BCIO:044056</t>
+          <t>BCIO:044055</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>communication using selected words from a second language</t>
+          <t>communication avoiding offensive language</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>A communication using occasional words chosen from a language spoken by both the instigator and the recipient that is not the main language.</t>
+          <t>A communication using language chosen by the instigator to avoid using words or phrases that could be perceived as rude or insulting.</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -2752,19 +2767,19 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BCIO:044052</t>
+          <t>BCIO:044056</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>communication using non-pressurising language</t>
+          <t>communication using selected words from a second language</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>A communication using language chosen to avoid coercing or persuading the recipient to think, feel or behave in a certain manner.</t>
+          <t>A communication using occasional words chosen from a language spoken by both the instigator and the recipient that is not the main language.</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -2776,19 +2791,19 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BCIO:044010</t>
+          <t>BCIO:044054</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>affirming communication</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>communication using specialist language</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>A communication involving acknowledging another's strength or resilience in a given context or situation.</t>
+          <t>A communication using words or expressions used by a profession or group that are difficult for others not in that profession or group to understand.</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -2796,85 +2811,105 @@
           <t>style of delivery</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Making explicit statements of partnership or support; Shows approval;</t>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>using jargon</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BCIO:044022</t>
+          <t>BCIO:044018</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>communication adding intensity to another's views</t>
+          <t>branded communication</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>A communication using statements that add intensity to the content or emotion expressed by another person.</t>
+          <t>A communication using a consistent style of text or graphics to identify and distinguish a product, service or intervention from other products, services or interventions.</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Change for Life, Time to Change, NHS Smokefree</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>use of branding; brand identity</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BCIO:044041</t>
+          <t>BCIO:044059</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>communication offering choice</t>
+          <t>emotionally expressive communication</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>A communication involving the initiator offering a range of options to the recipient.</t>
+          <t>A communication in a manner which clearly conveys the emotions of the initiator.</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BCIO:044039</t>
+          <t>BCIO:044034</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>communication involving confirmatory rephrasing</t>
+          <t>communication highlighting a contradiction</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>A communication involving the initiator rephrasing what a recipient says in a manner intended to confirm understanding of the recipient's situation rather than confront.</t>
+          <t>A communication pointing out a situation in which actions or propositions are inconsistent with each other.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BCIO:044028</t>
+          <t>BCIO:044049</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>communication encouraging discussion</t>
+          <t>communication using interjections to signal attentiveness</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>A communication in which the initiator promotes an extended two-way discussion regarding a topic.</t>
+          <t>A communication in which one person uses brief interjections to signal that they are listening to what the other person is saying.</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -2882,349 +2917,379 @@
           <t>style of delivery</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Words like "interesting", "yeah"," mmhmm"</t>
+        </is>
+      </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Contrasts with a more one-way, didactic style</t>
+          <t>"Back-channels" or "undertalk" in the Roter Interaction Analysis System</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>An interjection is a word, phrase or exclamation which is typically unconnected to a sentence and is used to express an emotion or reaction.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BCIO:044001</t>
+          <t>BCIO:044062</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>intervention content communication process</t>
+          <t>communication avoiding interrupting</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>A communication that transmits the content of an intervention</t>
+          <t>A communication in which at least one participant endeavours to not interject before another participant has finished making their point.</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>Note that an intervention is a planned process with the aim of influencing some outcome whereas a behaviour change intervention is an intervention that aims to influence human behaviour as an outcome.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BCIO:044002</t>
+          <t>BCIO:044036</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>behaviour change intervention content communication process</t>
-        </is>
-      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>communication involving acceptance that recipients views may be different to the initiator's views</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>An intervention content communication process that is about behaviour change intervention content</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A behaviour change intervention is a planned process that aims to influence human behaviour.  In contrast, an intervention is a planned process with the aim of influencing some outcome.  This outcome may be other than human behaviour. </t>
+          <t>A communication involving accepting that the recipient has different beliefs to the initiator and continuing with the planned activities while allowing both views to exist.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BCIO:044061</t>
+          <t>BCIO:044041</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>interrupting</t>
+          <t>communication offering choice</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>A communication in which one person interjects before another has finished making their point.</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication involving the initiator offering a range of options to the recipient.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BCIO:044009</t>
+          <t>BCIO:044048</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>active listening</t>
+          <t>communication using deliberate pauses</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>A communication involving one participant paying close attention to what is said by another, asking questions and reflecting as needed, in an attempt to fully understand what has been said.</t>
+          <t>A communication in which the speaker purposely leaves gaps between or after their speech utterances.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
           <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>staying silent (where this is intended to give others the chance to speak)</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Pauses may be deliberately left to provide opportunities for others to speak or reflect, or to demonstrate non-directiveness.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BCIO:044034</t>
+          <t>BCIO:044027</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>communication highlighting a contradiction</t>
+          <t>communication checking for own understanding</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>A communication pointing out a situation in which actions or propositions are inconsistent with each other.</t>
+          <t>A communication in which the instigator asks questions to determine if they have correctly comprehended the information presented by another.</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>clarifying what another has said</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BCIO:044012</t>
+          <t>BCIO:044028</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>asking questions</t>
+          <t>communication encouraging discussion</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>A communication in which some participant requests information from another participant.</t>
+          <t>A communication in which the initiator promotes an extended two-way discussion regarding a topic.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
           <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Contrasts with a more one-way, didactic style</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BCIO:044015</t>
+          <t>BCIO:044024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>asking leading questions</t>
-        </is>
-      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>communication avoiding argumentation</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Asking questions designed to prompt the questionee to answer in a specific, pre-determined manner.</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>asking directive questions</t>
+          <t>A communication which aims to focus on the feelings of others without debating the truth or falsity of statements or ideas.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BCIO:044014</t>
+          <t>BCIO:044061</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>asking focused questions</t>
-        </is>
-      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>interrupting</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Asking questions designed to narrow discussion to focus on a particular aspect or topic.</t>
+          <t>A communication in which one person interjects before another has finished making their point.</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BCIO:044013</t>
+          <t>BCIO:044035</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>asking closed-ended questions</t>
-        </is>
-      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>communication inviting reactions to content presented</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Asking questions that can only be answered with a limited set of responses.</t>
+          <t>A communication seeking information about a person's responses to the  content presented.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BCIO:050382</t>
+          <t>BCIO:044011</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>asking clarifying questions</t>
-        </is>
-      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>agenda-sharing communication</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Asking questions in order to better understand an issue.</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication in which the initiator and one or more activity participants work together to determine a focus for the activity to be undertaken.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BCIO:044016</t>
+          <t>BCIO:044039</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>asking open-ended questions</t>
-        </is>
-      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>communication involving confirmatory rephrasing</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Asking questions that cannot be answered with a simple yes or no, but instead require the questionee to elaborate on their points.</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication involving the initiator rephrasing what a recipient says in a manner intended to confirm understanding of the recipient's situation rather than confront.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BCIO:044024</t>
+          <t>BCIO:044124</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>communication avoiding argumentation</t>
+          <t>relationship building</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>A communication which aims to focus on the feelings of others without debating the truth or falsity of statements or ideas.</t>
+          <t>A communication aimed at building or managing aspects of the interpersonal relationship between an initiator and a recipient rather than focusing on delivering communication content.</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>offering contact, inviting patient to contact you in the event of difficulties or questions</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BCIO:044011</t>
+          <t>BCIO:044010</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>agenda-sharing communication</t>
+          <t>affirming communication</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>A communication in which the initiator and one or more activity participants work together to determine a focus for the activity to be undertaken.</t>
+          <t>A communication involving acknowledging another's strength or resilience in a given context or situation.</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Making explicit statements of partnership or support; Shows approval;</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BCIO:044040</t>
+          <t>BCIO:044047</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>communication involving elaboration of arguments</t>
+          <t>communication using commands</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>A communication further developing a declarative statement that has been made  by making it clearer, more precise, bringing out its consequences or giving a concrete example.</t>
+          <t>A communication using statements that order or direct a person to think or behave in a certain way.</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>communication using imperatives</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BCIO:044018</t>
+          <t>BCIO:044019</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>branded communication</t>
+          <t>discussion</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>A communication using a consistent style of text or graphics to identify and distinguish a product, service or intervention from other products, services or interventions.</t>
+          <t>A communication involving an extended exchange of utterances between an instigator and at least one other person.</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -3232,183 +3297,138 @@
           <t>style of delivery</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>Change for Life, Time to Change, NHS Smokefree</t>
-        </is>
-      </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>use of branding; brand identity</t>
+          <t>An utterance is an uninterrupted stretch of speech or writing produced by an individual on a particular occasion. An utterance can range from a single word to a complete sentence.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BCIO:044030</t>
+          <t>BCIO:044020</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>exploring communication</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>classroom-style discussion</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>A communication to better understand what a person thinks or feels about a topic or an experience.</t>
+          <t>A discussion led by the initiator in a manner typical of a teacher or lecturer.</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>eliciting or seeking information</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>This can include asking questions or prompting elaboration e.g 'Tell me more about that'</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BCIO:050385</t>
+          <t>BCIO:044037</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>communication exploring a person's feelings about an experience</t>
-        </is>
-      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>communication involving agreement</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>An exploring communication focused on a person's affective responses to an experience.</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>An experience can be any situation or state a person encounters or undergoes</t>
+          <t>A communication in which one participant concurs with the views stated by another.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BCIO:050386</t>
+          <t>BCIO:044038</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>communication exploring a person's thoughts about a topic</t>
+          <t>communication involving agreement followed by highlighting incongruent aspects</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>An exploring communication focused on what a person thinks about a matter.</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>clarifying what someone has said</t>
+          <t>A communication involving agreement in which one participant concurs with the views stated by another and then points out an incongruent aspect of the situation under discussion.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BCIO:050387</t>
+          <t>BCIO:044026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>communication exploring a person's thoughts about an experience</t>
-        </is>
-      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>communication checking for others' understanding</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>An exploring communication focused on what a person thinks about an experience.</t>
+          <t>A communication in which the instigator asks questions to determine if the recipient has comprehended information that has been presented.</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>An experience can be any situation or state a person encounters or undergoes</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BCIO:050383</t>
+          <t>BCIO:044064</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>communication exploring a person's feelings about a topic</t>
-        </is>
-      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>narrative communication</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>An exploring communication focused on a person's affective responses to a matter.</t>
+          <t>A communication describing the particulars of a person's life or a course of events in the style of telling a story.</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>Elicit concerns, problems and reactions</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BCIO:044047</t>
+          <t>BCIO:044017</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>communication using commands</t>
+          <t>banter</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>A communication using statements that order or direct a person to think or behave in a certain way.</t>
+          <t>A communication involving the exchange of light and teasing remarks intended to be playful.</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -3418,257 +3438,232 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>communication using imperatives</t>
+          <t>Note that teasing is an essential part of the definition of banter. For amusing or enjoyable communication, but without the element of teasing, using entertaining or humourous communication style. Also, note that banter may not always be perceived as playful by the subject of the remarks</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BCIO:044029</t>
+          <t>BCIO:050388</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>communication evoking another's ideas about change</t>
+          <t>communication showing acknowledgement</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>A communication in which the initiator attempts to elicit the recipient’s own thoughts and ideas about change rather than imposing the initiator’s own opinion.</t>
+          <t>A communication involving the expressed recognition of what another has expressed.</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>evoking change talk in motivational interviewing</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BCIO:044042</t>
+          <t>BCIO:044021</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>communication understating intensity of person's views</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>communication acknowledging difficulties</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>A communication using statements that diminish or understate the intensity of the content or emotion expressed by the other person.</t>
+          <t>A communication showing acknolwedgement conveying empathy or compassion towards a sub-optimal situation or concerns of a recipient.</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>"undershooting" in motivational interviewing</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BCIO:044060</t>
+          <t>BCIO:044078</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>guiding communication</t>
+          <t>shifting focus of communication</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>A communication that involves suggesting adoption of certain beliefs, theories or lines of action by others.</t>
+          <t>A communication that involves altering the area of greatest attention during the delivery of information.</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">When a practitioner suggests to a patient 'Could you think about it like this...' </t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BCIO:044037</t>
+          <t>BCIO:044060</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>communication involving agreement</t>
+          <t>guiding communication</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>A communication in which one participant concurs with the views stated by another.</t>
+          <t>A communication that involves suggesting adoption of certain beliefs, theories or lines of action by others.</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">When a practitioner suggests to a patient 'Could you think about it like this...' </t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BCIO:044038</t>
+          <t>BCIO:044022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
-      <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>communication involving agreement followed by highlighting incongruent aspects</t>
-        </is>
-      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>communication adding intensity to another's views</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>A communication involving agreement in which one participant concurs with the views stated by another and then points out an incongruent aspect of the situation under discussion.</t>
+          <t>A communication using statements that add intensity to the content or emotion expressed by another person.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BCIO:044036</t>
+          <t>BCIO:044012</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>communication involving acceptance that recipients views may be different to the initiator's views</t>
+          <t>asking questions</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>A communication involving accepting that the recipient has different beliefs to the initiator and continuing with the planned activities while allowing both views to exist.</t>
+          <t>A communication in which some participant requests information from another participant.</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BCIO:044035</t>
+          <t>BCIO:044014</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>communication inviting reactions to content presented</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>asking focused questions</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>A communication seeking information about a person's responses to the  content presented.</t>
+          <t>Asking questions designed to narrow discussion to focus on a particular aspect or topic.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BCIO:044069</t>
+          <t>BCIO:044013</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>offering reassurance</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>asking closed-ended questions</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>A communication intended to provide hope and strength in times of anxiety, worry, confusion, grief, distress, or suffering.</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>made reassuring statements</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>based on Roter Interactional Analysis System</t>
+          <t>Asking questions that can only be answered with a limited set of responses.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BCIO:044048</t>
+          <t>BCIO:044016</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>communication using deliberate pauses</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>asking open-ended questions</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>A communication in which the speaker purposely leaves gaps between or after their speech utterances.</t>
+          <t>Asking questions that cannot be answered with a simple yes or no, but instead require the questionee to elaborate on their points.</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>staying silent (where this is intended to give others the chance to speak)</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>Pauses may be deliberately left to provide opportunities for others to speak or reflect, or to demonstrate non-directiveness.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BCIO:044078</t>
+          <t>BCIO:050382</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>shifting focus of communication</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>asking clarifying questions</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>A communication that involves altering the area of greatest attention during the delivery of information.</t>
+          <t>Asking questions in order to better understand an issue.</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -3680,19 +3675,19 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BCIO:044019</t>
+          <t>BCIO:044015</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>discussion</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>asking leading questions</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>A communication involving an extended exchange of utterances between an instigator and at least one other person.</t>
+          <t>Asking questions designed to prompt the questionee to answer in a specific, pre-determined manner.</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -3702,50 +3697,45 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>An utterance is an uninterrupted stretch of speech or writing produced by an individual on a particular occasion. An utterance can range from a single word to a complete sentence.</t>
+          <t>asking directive questions</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BCIO:044020</t>
+          <t>BCIO:044023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>classroom-style discussion</t>
-        </is>
-      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>communication asking permission to provide information and advice</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>A discussion led by the initiator in a manner typical of a teacher or lecturer.</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication which involves asking for approval before sharing knowledge and giving guidance.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BCIO:044027</t>
+          <t>BCIO:044069</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>communication checking for own understanding</t>
+          <t>offering reassurance</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>A communication in which the instigator asks questions to determine if they have correctly comprehended the information presented by another.</t>
+          <t>A communication intended to provide hope and strength in times of anxiety, worry, confusion, grief, distress, or suffering.</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -3755,26 +3745,31 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>clarifying what another has said</t>
+          <t>made reassuring statements</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>based on Roter Interactional Analysis System</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BCIO:044062</t>
+          <t>BCIO:044009</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>communication avoiding interrupting</t>
+          <t>active listening</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>A communication in which at least one participant endeavours to not interject before another participant has finished making their point.</t>
+          <t>A communication involving one participant paying close attention to what is said by another, asking questions and reflecting as needed, in an attempt to fully understand what has been said.</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -3786,19 +3781,19 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BCIO:044065</t>
+          <t>BCIO:044071</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>negotiation</t>
+          <t>reflective communication</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>A communication involving goal-oriented collaboration to arrive at an agreement or compromise on a matter of importance to the individuals involved.</t>
+          <t>A communication presenting a person's previously expressed thoughts and feelings back to them.</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -3810,67 +3805,77 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BCIO:044064</t>
+          <t>BCIO:044075</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>narrative communication</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>emotion-emphasising reflective communication</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>A communication describing the particulars of a person's life or a course of events in the style of telling a story.</t>
+          <t>A reflective communication highlighting the emotional aspects of an issue as previously described by the recipient.</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
           <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>"reflection of feeling" in Motivational Interviewing</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BCIO:044071</t>
+          <t>BCIO:044076</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>reflective communication</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>re-evaluation prompting reflective communication</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>A communication presenting a person's previously expressed thoughts and feelings back to them.</t>
+          <t>A reflective communication in which the instigator restates the recipient's prior assertation in a less credible way to prompt reconsideration of the assertion.</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
           <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>"amplified reflection" in Motivational Interviewing</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BCIO:044075</t>
+          <t>BCIO:044072</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>emotion-emphasising reflective communication</t>
+          <t>summarising reflective communication</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>A reflective communication highlighting the emotional aspects of an issue as previously described by the recipient.</t>
+          <t>A reflective communication in which the instigator pulls together key points from a complex story told by the recipient in a succinct restatement.</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -3878,28 +3883,28 @@
           <t>style of delivery</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>"reflection of feeling" in Motivational Interviewing</t>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>"summarising reflection" in Motivational Interviewing</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BCIO:044076</t>
+          <t>BCIO:044074</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>re-evaluation prompting reflective communication</t>
+          <t>metaphor-using reflective communication</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator restates the recipient's prior assertation in a less credible way to prompt reconsideration of the assertion.</t>
+          <t>A reflective communication in which the instigator  replaces a word or phrase of the recipient's prior assertion with a figure of speech suggesting an analogy.</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -3907,28 +3912,28 @@
           <t>style of delivery</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>"amplified reflection" in Motivational Interviewing</t>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>"metaphorical reflection" in Motivational Interviewing</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BCIO:044074</t>
+          <t>BCIO:044073</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>metaphor-using reflective communication</t>
+          <t>double-sided reflective communication</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator  replaces a word or phrase of the recipient's prior assertion with a figure of speech suggesting an analogy.</t>
+          <t>A reflective communication in which the instigator aims to highlight both the positive and negative sides of an issue as previously expressed by the recipient.</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -3936,28 +3941,28 @@
           <t>style of delivery</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>"metaphorical reflection" in Motivational Interviewing</t>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>"double-sided reflection" in Motivational Interviewing</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BCIO:044072</t>
+          <t>BCIO:044077</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>summarising reflective communication</t>
-        </is>
-      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>script-based communication</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator pulls together key points from a complex story told by the recipient in a succinct restatement.</t>
+          <t>A communication which follows a pre-written sequence of instructions that are interpreted or carried out by a person or by a program.</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -3967,26 +3972,26 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>"summarising reflection" in Motivational Interviewing</t>
+          <t>This class involves tightly following a set of written instructions. It is different to structured communication style, which is a pre-planned style but not to the extent of using a written script.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BCIO:044073</t>
+          <t>BCIO:044001</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>double-sided reflective communication</t>
-        </is>
-      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>intervention content communication process</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator aims to highlight both the positive and negative sides of an issue as previously expressed by the recipient.</t>
+          <t>A communication that transmits the content of an intervention</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -3996,103 +4001,108 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>"double-sided reflection" in Motivational Interviewing</t>
+          <t>Note that an intervention is a planned process with the aim of influencing some outcome whereas a behaviour change intervention is an intervention that aims to influence human behaviour as an outcome.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BCIO:050388</t>
+          <t>BCIO:044002</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>communication showing acknowledgement</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>behaviour change intervention content communication process</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>A communication involving the expressed recognition of what another has expressed.</t>
+          <t>An intervention content communication process that is about behaviour change intervention content</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
           <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A behaviour change intervention is a planned process that aims to influence human behaviour.  In contrast, an intervention is a planned process with the aim of influencing some outcome.  This outcome may be other than human behaviour. </t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BCIO:044021</t>
+          <t>BCIO:044042</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>communication acknowledging difficulties</t>
-        </is>
-      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>communication understating intensity of person's views</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>A communication showing acknolwedgement conveying empathy or compassion towards a sub-optimal situation or concerns of a recipient.</t>
+          <t>A communication using statements that diminish or understate the intensity of the content or emotion expressed by the other person.</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
           <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>"undershooting" in motivational interviewing</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BCIO:044043</t>
+          <t>BCIO:044058</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>communication using a particular form of address</t>
+          <t>communication using rational arguments</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a certain name or title to refer to that person.</t>
+          <t>A communication that involves the use of declarative propositions based on what the communicator believes to be logical.</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>The child classes of this class are specific types of address, whereas this class is for a non-specific type of address.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BCIO:044044</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr"/>
+          <t>BCIO:050552</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>communication channel</t>
+        </is>
+      </c>
       <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>communication using formal address</t>
-        </is>
-      </c>
+      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a formal, legal or official name or title to refer to that person.</t>
+          <t>A &lt;process&gt; by which a communication is delivered.</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -4104,48 +4114,43 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BCIO:044046</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr"/>
+          <t>BCIO:050457</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>expressive behaviour</t>
+        </is>
+      </c>
       <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>communication using preferred form of address</t>
-        </is>
-      </c>
+      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a name or title that the person has specified the instigator should use.</t>
+          <t>An individual human behaviour that conveys a thought or feeling.</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>Depending on whether Suzie Jones prefers to be addressed formally, or by her given name, saying either "Hello Mrs Jones" or "Hello Suzie"</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BCIO:044045</t>
+          <t>BCIO:036034</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>communication using informal address</t>
-        </is>
-      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>human communication behaviour</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a casual or colloquial name or title to refer to that person.</t>
+          <t>An expressive behaviour that involves the transmission of information between two or more people.</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -4157,19 +4162,19 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BCIO:044026</t>
+          <t>BCIO:050237</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>communication checking for others' understanding</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>linguistic communication behaviour</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>A communication in which the instigator asks questions to determine if the recipient has comprehended information that has been presented.</t>
+          <t>A human communication behaviour in which the information that is communicated is encoded in language.</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -4181,48 +4186,43 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BCIO:044077</t>
+          <t>BCIO:050374</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>script-based communication</t>
+          <t>laughing</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>A communication which follows a pre-written sequence of instructions that are interpreted or carried out by a person or by a program.</t>
+          <t>An expressive behaviour showing elation, amusement or scorn by means of facial expressions and repeated sharp exhalations.</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
           <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>This class involves tightly following a set of written instructions. It is different to structured communication style, which is a pre-planned style but not to the extent of using a written script.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BCIO:050552</t>
+          <t>BCIO:050555</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>communication channel</t>
+          <t>communication message</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>A &lt;process&gt; by which a communication is delivered.</t>
+          <t>An &lt;information content entity&gt; transmitted from a communication source to a communication recipient.</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">

--- a/StyleOfDelivery/BCIO-style-hierarchy.xlsx
+++ b/StyleOfDelivery/BCIO-style-hierarchy.xlsx
@@ -587,7 +587,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>dose range specification</t>
+          <t>spécification d’intervalle de dose</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -598,7 +598,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>An information content entity that specifies the minimum and maximum quantities of drug product or active ingredient in a dose administration.</t>
+          <t>Une entité de contenu informationnel qui spécifie les quantités minimum et maximum de médicament ou d’ingrédient actif dans une administration de dose.</t>
         </is>
       </c>
     </row>
@@ -15971,7 +15971,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>BCIO:015317</t>
+          <t>BCIO:015392</t>
         </is>
       </c>
       <c r="B598" t="inlineStr"/>
@@ -15981,7 +15981,7 @@
       <c r="F598" t="inlineStr"/>
       <c r="G598" t="inlineStr">
         <is>
-          <t>expertise discipline population statistic</t>
+          <t>history of exposure to an occupational hazard population statistic</t>
         </is>
       </c>
       <c r="H598" t="inlineStr"/>
@@ -15990,14 +15990,14 @@
       <c r="K598" t="inlineStr"/>
       <c r="L598" t="inlineStr">
         <is>
-          <t>A population statistic about expertise discipline.</t>
+          <t>A population statistic about history of exposure to an occupational hazard.</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>BCIO:015287</t>
+          <t>BCIO:015393</t>
         </is>
       </c>
       <c r="B599" t="inlineStr"/>
@@ -16008,7 +16008,7 @@
       <c r="G599" t="inlineStr"/>
       <c r="H599" t="inlineStr">
         <is>
-          <t>discipline of current programme of study or training population statistic</t>
+          <t>percentage history of exposure to an occupational hazard population statistic</t>
         </is>
       </c>
       <c r="I599" t="inlineStr"/>
@@ -16016,14 +16016,14 @@
       <c r="K599" t="inlineStr"/>
       <c r="L599" t="inlineStr">
         <is>
-          <t>A population statistic about discipline of current programme of study or training.</t>
+          <t>A(n) history of exposure to an occupational hazard population statistic that is the percentage of people that have a history of exposure to an occupational hazard in the population.</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>BCIO:015288</t>
+          <t>BCIO:015394</t>
         </is>
       </c>
       <c r="B600" t="inlineStr"/>
@@ -16032,24 +16032,24 @@
       <c r="E600" t="inlineStr"/>
       <c r="F600" t="inlineStr"/>
       <c r="G600" t="inlineStr"/>
-      <c r="H600" t="inlineStr"/>
-      <c r="I600" t="inlineStr">
-        <is>
-          <t>percentage discipline of current programme of study or training population statistic</t>
-        </is>
-      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>proportion history of exposure to an occupational hazard population statistic</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr"/>
       <c r="J600" t="inlineStr"/>
       <c r="K600" t="inlineStr"/>
       <c r="L600" t="inlineStr">
         <is>
-          <t>A(n) discipline of current programme of study or training population statistic that is the percentage of people that have a discipline of current programme of study or training in the population.</t>
+          <t>A(n) history of exposure to an occupational hazard population statistic that is the proportion of people that have a history of exposure to an occupational hazard in the population.</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>BCIO:015289</t>
+          <t>BCIO:015317</t>
         </is>
       </c>
       <c r="B601" t="inlineStr"/>
@@ -16057,25 +16057,25 @@
       <c r="D601" t="inlineStr"/>
       <c r="E601" t="inlineStr"/>
       <c r="F601" t="inlineStr"/>
-      <c r="G601" t="inlineStr"/>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>expertise discipline population statistic</t>
+        </is>
+      </c>
       <c r="H601" t="inlineStr"/>
-      <c r="I601" t="inlineStr">
-        <is>
-          <t>proportion discipline of current programme of study or training population statistic</t>
-        </is>
-      </c>
+      <c r="I601" t="inlineStr"/>
       <c r="J601" t="inlineStr"/>
       <c r="K601" t="inlineStr"/>
       <c r="L601" t="inlineStr">
         <is>
-          <t>A(n) discipline of current programme of study or training population statistic that is the proportion of people that have a discipline of current programme of study or training in the population.</t>
+          <t>A population statistic about expertise discipline.</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>BCIO:015319</t>
+          <t>BCIO:015287</t>
         </is>
       </c>
       <c r="B602" t="inlineStr"/>
@@ -16086,7 +16086,7 @@
       <c r="G602" t="inlineStr"/>
       <c r="H602" t="inlineStr">
         <is>
-          <t>proportion expertise discipline population statistic</t>
+          <t>discipline of current programme of study or training population statistic</t>
         </is>
       </c>
       <c r="I602" t="inlineStr"/>
@@ -16094,14 +16094,14 @@
       <c r="K602" t="inlineStr"/>
       <c r="L602" t="inlineStr">
         <is>
-          <t>A(n) expertise discipline population statistic that is the proportion of people that have a expertise discipline in the population.</t>
+          <t>A population statistic about discipline of current programme of study or training.</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>BCIO:015318</t>
+          <t>BCIO:015288</t>
         </is>
       </c>
       <c r="B603" t="inlineStr"/>
@@ -16110,24 +16110,24 @@
       <c r="E603" t="inlineStr"/>
       <c r="F603" t="inlineStr"/>
       <c r="G603" t="inlineStr"/>
-      <c r="H603" t="inlineStr">
-        <is>
-          <t>percentage expertise discipline population statistic</t>
-        </is>
-      </c>
-      <c r="I603" t="inlineStr"/>
+      <c r="H603" t="inlineStr"/>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>percentage discipline of current programme of study or training population statistic</t>
+        </is>
+      </c>
       <c r="J603" t="inlineStr"/>
       <c r="K603" t="inlineStr"/>
       <c r="L603" t="inlineStr">
         <is>
-          <t>A(n) expertise discipline population statistic that is the percentage of people that have a expertise discipline in the population.</t>
+          <t>A(n) discipline of current programme of study or training population statistic that is the percentage of people that have a discipline of current programme of study or training in the population.</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>BCIO:015290</t>
+          <t>BCIO:015289</t>
         </is>
       </c>
       <c r="B604" t="inlineStr"/>
@@ -16136,24 +16136,24 @@
       <c r="E604" t="inlineStr"/>
       <c r="F604" t="inlineStr"/>
       <c r="G604" t="inlineStr"/>
-      <c r="H604" t="inlineStr">
-        <is>
-          <t>discipline of highest level of formal educational qualification achieved population statistic</t>
-        </is>
-      </c>
-      <c r="I604" t="inlineStr"/>
+      <c r="H604" t="inlineStr"/>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>proportion discipline of current programme of study or training population statistic</t>
+        </is>
+      </c>
       <c r="J604" t="inlineStr"/>
       <c r="K604" t="inlineStr"/>
       <c r="L604" t="inlineStr">
         <is>
-          <t>A population statistic about discipline of highest level of formal educational qualification achieved.</t>
+          <t>A(n) discipline of current programme of study or training population statistic that is the proportion of people that have a discipline of current programme of study or training in the population.</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>BCIO:015292</t>
+          <t>BCIO:015319</t>
         </is>
       </c>
       <c r="B605" t="inlineStr"/>
@@ -16162,24 +16162,24 @@
       <c r="E605" t="inlineStr"/>
       <c r="F605" t="inlineStr"/>
       <c r="G605" t="inlineStr"/>
-      <c r="H605" t="inlineStr"/>
-      <c r="I605" t="inlineStr">
-        <is>
-          <t>proportion discipline of highest level of formal educational qualification achieved population statistic</t>
-        </is>
-      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>proportion expertise discipline population statistic</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr"/>
       <c r="J605" t="inlineStr"/>
       <c r="K605" t="inlineStr"/>
       <c r="L605" t="inlineStr">
         <is>
-          <t>A(n) discipline of highest level of formal educational qualification achieved population statistic that is the proportion of people that have a discipline of highest level of formal educational qualification achieved in the population.</t>
+          <t>A(n) expertise discipline population statistic that is the proportion of people that have a expertise discipline in the population.</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>BCIO:015291</t>
+          <t>BCIO:015318</t>
         </is>
       </c>
       <c r="B606" t="inlineStr"/>
@@ -16188,24 +16188,24 @@
       <c r="E606" t="inlineStr"/>
       <c r="F606" t="inlineStr"/>
       <c r="G606" t="inlineStr"/>
-      <c r="H606" t="inlineStr"/>
-      <c r="I606" t="inlineStr">
-        <is>
-          <t>percentage discipline of highest level of formal educational qualification achieved population statistic</t>
-        </is>
-      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>percentage expertise discipline population statistic</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr"/>
       <c r="J606" t="inlineStr"/>
       <c r="K606" t="inlineStr"/>
       <c r="L606" t="inlineStr">
         <is>
-          <t>A(n) discipline of highest level of formal educational qualification achieved population statistic that is the percentage of people that have a discipline of highest level of formal educational qualification achieved in the population.</t>
+          <t>A(n) expertise discipline population statistic that is the percentage of people that have a expertise discipline in the population.</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>BCIO:015392</t>
+          <t>BCIO:015290</t>
         </is>
       </c>
       <c r="B607" t="inlineStr"/>
@@ -16213,25 +16213,25 @@
       <c r="D607" t="inlineStr"/>
       <c r="E607" t="inlineStr"/>
       <c r="F607" t="inlineStr"/>
-      <c r="G607" t="inlineStr">
-        <is>
-          <t>history of exposure to an occupational hazard population statistic</t>
-        </is>
-      </c>
-      <c r="H607" t="inlineStr"/>
+      <c r="G607" t="inlineStr"/>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>discipline of highest level of formal educational qualification achieved population statistic</t>
+        </is>
+      </c>
       <c r="I607" t="inlineStr"/>
       <c r="J607" t="inlineStr"/>
       <c r="K607" t="inlineStr"/>
       <c r="L607" t="inlineStr">
         <is>
-          <t>A population statistic about history of exposure to an occupational hazard.</t>
+          <t>A population statistic about discipline of highest level of formal educational qualification achieved.</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>BCIO:015393</t>
+          <t>BCIO:015292</t>
         </is>
       </c>
       <c r="B608" t="inlineStr"/>
@@ -16240,24 +16240,24 @@
       <c r="E608" t="inlineStr"/>
       <c r="F608" t="inlineStr"/>
       <c r="G608" t="inlineStr"/>
-      <c r="H608" t="inlineStr">
-        <is>
-          <t>percentage history of exposure to an occupational hazard population statistic</t>
-        </is>
-      </c>
-      <c r="I608" t="inlineStr"/>
+      <c r="H608" t="inlineStr"/>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>proportion discipline of highest level of formal educational qualification achieved population statistic</t>
+        </is>
+      </c>
       <c r="J608" t="inlineStr"/>
       <c r="K608" t="inlineStr"/>
       <c r="L608" t="inlineStr">
         <is>
-          <t>A(n) history of exposure to an occupational hazard population statistic that is the percentage of people that have a history of exposure to an occupational hazard in the population.</t>
+          <t>A(n) discipline of highest level of formal educational qualification achieved population statistic that is the proportion of people that have a discipline of highest level of formal educational qualification achieved in the population.</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>BCIO:015394</t>
+          <t>BCIO:015291</t>
         </is>
       </c>
       <c r="B609" t="inlineStr"/>
@@ -16266,17 +16266,17 @@
       <c r="E609" t="inlineStr"/>
       <c r="F609" t="inlineStr"/>
       <c r="G609" t="inlineStr"/>
-      <c r="H609" t="inlineStr">
-        <is>
-          <t>proportion history of exposure to an occupational hazard population statistic</t>
-        </is>
-      </c>
-      <c r="I609" t="inlineStr"/>
+      <c r="H609" t="inlineStr"/>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>percentage discipline of highest level of formal educational qualification achieved population statistic</t>
+        </is>
+      </c>
       <c r="J609" t="inlineStr"/>
       <c r="K609" t="inlineStr"/>
       <c r="L609" t="inlineStr">
         <is>
-          <t>A(n) history of exposure to an occupational hazard population statistic that is the proportion of people that have a history of exposure to an occupational hazard in the population.</t>
+          <t>A(n) discipline of highest level of formal educational qualification achieved population statistic that is the percentage of people that have a discipline of highest level of formal educational qualification achieved in the population.</t>
         </is>
       </c>
     </row>
@@ -18398,7 +18398,7 @@
       <c r="K691" t="inlineStr"/>
       <c r="L691" t="inlineStr">
         <is>
-          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
+          <t>An &lt;independent continuant&gt; that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       <c r="E707" t="inlineStr"/>
       <c r="F707" t="inlineStr">
         <is>
-          <t>human being</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G707" t="inlineStr"/>
@@ -20691,7 +20691,7 @@
       <c r="K779" t="inlineStr"/>
       <c r="L779" t="inlineStr">
         <is>
-          <t>A person who is between the ages of  13 and 19.</t>
+          <t>A person between 13 and 19 years of age.</t>
         </is>
       </c>
     </row>
@@ -21427,7 +21427,7 @@
       <c r="G808" t="inlineStr"/>
       <c r="H808" t="inlineStr">
         <is>
-          <t>pharmacy facility</t>
+          <t>établissement de pharmacologie</t>
         </is>
       </c>
       <c r="I808" t="inlineStr"/>
@@ -22022,7 +22022,7 @@
       <c r="D831" t="inlineStr"/>
       <c r="E831" t="inlineStr">
         <is>
-          <t>fiat object part</t>
+          <t>fiat object</t>
         </is>
       </c>
       <c r="F831" t="inlineStr"/>
@@ -22328,7 +22328,7 @@
       <c r="C843" t="inlineStr"/>
       <c r="D843" t="inlineStr">
         <is>
-          <t>realizable entity</t>
+          <t>realizable</t>
         </is>
       </c>
       <c r="E843" t="inlineStr"/>
@@ -22543,7 +22543,7 @@
       <c r="K851" t="inlineStr"/>
       <c r="L851" t="inlineStr">
         <is>
-          <t>A disposition that inheres in some extended organism.</t>
+          <t>A bodily disposition is a disposition that inheres in some extended organism. Examples are: my disposition to catch a cold when exposed to a virus, my ability to speak the English language.</t>
         </is>
       </c>
     </row>
@@ -22933,7 +22933,7 @@
       <c r="K866" t="inlineStr"/>
       <c r="L866" t="inlineStr">
         <is>
-          <t>A bodily disposition that is realized in a mental process.</t>
+          <t>A &lt;bodily disposition&gt; that is realized in a mental process.</t>
         </is>
       </c>
     </row>
@@ -23885,7 +23885,7 @@
       <c r="K903" t="inlineStr"/>
       <c r="L903" t="inlineStr">
         <is>
-          <t>A personal attribute reflecting a person's economic and social position in relation to others, based on their income, education, or occupation.</t>
+          <t>The personal information that indicates an individual's or his/her family's economic and social position in relation to others, based on income, education, and occupation.</t>
         </is>
       </c>
     </row>
@@ -25003,7 +25003,7 @@
       <c r="K946" t="inlineStr"/>
       <c r="L946" t="inlineStr">
         <is>
-          <t>A bodily quality is a quality that inheres in some extended organism.</t>
+          <t>A quality that inheres in some extended organism.</t>
         </is>
       </c>
     </row>
@@ -26251,7 +26251,7 @@
       <c r="K994" t="inlineStr"/>
       <c r="L994" t="inlineStr">
         <is>
-          <t>A personal attribute reflecting a person's economic and social position in relation to others, based on their income, education, or occupation.</t>
+          <t>The personal information that indicates an individual's or his/her family's economic and social position in relation to others, based on income, education, and occupation.</t>
         </is>
       </c>
     </row>
@@ -26615,7 +26615,7 @@
       <c r="K1008" t="inlineStr"/>
       <c r="L1008" t="inlineStr">
         <is>
-          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
+          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
         </is>
       </c>
     </row>
@@ -39644,7 +39644,7 @@
       <c r="K1487" t="inlineStr"/>
       <c r="L1487" t="inlineStr">
         <is>
-          <t>A process in which at least one bodily component of an organsim participates.</t>
+          <t>A process in which at least one bodily component of an organism participates.</t>
         </is>
       </c>
     </row>
@@ -44307,7 +44307,7 @@
       <c r="K1665" t="inlineStr"/>
       <c r="L1665" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valence is a process profile of an emotion, mood, or affective bodily feeling (such as pleasure and pain). Valence can be positive or negative, with different strengths in both directions. For example, pleasure is positively valenced while pain is negatively valenced.  </t>
+          <t>A &lt;bodily process&gt; that occurs in the brain, and that can of itself be conscious, or can give rise to a process that can of itself be conscious or can give rise to behaviour.</t>
         </is>
       </c>
     </row>
@@ -45062,7 +45062,7 @@
       <c r="K1694" t="inlineStr"/>
       <c r="L1694" t="inlineStr">
         <is>
-          <t>The subjective emotional feeling is that (fiat) part of the emotion process by which the organism experiences its own emotion.</t>
+          <t>An &lt;affective process&gt; that involves the experience of internal or external sensory stimuli.</t>
         </is>
       </c>
     </row>
